--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2024/HAWAII_2024.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2024/HAWAII_2024.xlsx
@@ -357,22 +357,22 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Santa Bárbara</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -568,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -597,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Desconocido</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Álvaro Obregón</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Total</t>
@@ -703,7 +793,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Coahuila de Zaragoza</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -719,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Total</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Topia</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Total</t>
@@ -778,7 +883,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -794,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C31">
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -820,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C33">
@@ -833,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Sultepec</t>
@@ -846,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Salamanca</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Total</t>
@@ -923,7 +1068,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C40">
@@ -934,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>San Miguel Totolapan</t>
@@ -947,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Tlalchapa</t>
@@ -960,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Total</t>
@@ -991,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -1004,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C46">
@@ -1017,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1048,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Ameca</t>
@@ -1061,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Casimiro Castillo</t>
@@ -1074,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Desconocido</t>
@@ -1087,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Ejutla</t>
@@ -1100,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -1113,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>La Huerta</t>
@@ -1126,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>La Manzanilla de la Paz</t>
+          <t>La Manzanilla De La Paz</t>
         </is>
       </c>
       <c r="C55">
@@ -1139,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Mexticacán</t>
@@ -1152,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -1165,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tequila</t>
@@ -1178,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C59">
@@ -1191,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C60">
@@ -1204,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Totatiche</t>
@@ -1217,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -1230,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C63">
@@ -1243,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1258,7 +1513,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Michoacán de Ocampo</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1274,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cojumatlán de Régules</t>
+          <t>Cojumatlán De Régules</t>
         </is>
       </c>
       <c r="C66">
@@ -1287,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Indaparapeo</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1357,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -1370,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Tepalcingo</t>
@@ -1383,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1403,7 +1698,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ixtlán del Río</t>
+          <t>Ixtlán Del Río</t>
         </is>
       </c>
       <c r="C75">
@@ -1414,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>La Yesca</t>
@@ -1427,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -1440,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1460,7 +1770,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C79">
@@ -1471,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1491,7 +1806,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C81">
@@ -1502,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C82">
@@ -1515,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>San Agustín Chayuco</t>
@@ -1528,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>San Sebastián Río Hondo</t>
@@ -1541,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Santo Tomás Ocotepec</t>
@@ -1554,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1585,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Los Reyes de Juárez</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C88">
@@ -1598,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Naupan</t>
@@ -1611,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1624,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -1637,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -1650,9 +2015,14 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tetela de Ocampo</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C93">
@@ -1663,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1683,7 +2058,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C95">
@@ -1694,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1725,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1756,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -1769,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1784,7 +2179,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Veracruz de Ignacio de la Llave</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -1800,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -1813,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1844,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1864,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C107">
@@ -1875,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Villa García</t>
@@ -1888,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1903,7 +2323,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C110">
